--- a/projects/paper-01/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-01/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -658,9 +658,17 @@
           <t>10.1080/13825585.2019.1708251</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="3" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>N=42, 年龄67.9±5.5岁, WM训练(α-span, 2-back, 数字更新), RCT</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -694,9 +702,17 @@
           <t>10.1007/s00426-017-0961-8</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="3" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>N=72, 年龄范围65-75岁(论文未报告均值), WM训练+背景音乐, RCT</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -730,9 +746,17 @@
           <t>10.1080/13825585.2015.1031723</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="3" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>N=46, 均值64.8岁, 双n-back训练, RCT - 修正：均值≥60</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="n">
@@ -766,9 +790,17 @@
           <t>10.1371/journal.pone.0121904</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="3" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>N=72, 均值64.38岁, WM训练+tDCS, RCT - 修正：均值≥60</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -802,9 +834,17 @@
           <t>10.1002/brb3.1136</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="3" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>N=28老年人, 均值63.11岁, n-back训练+EEG, RCT - 混合研究老年人组符合</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -838,9 +878,17 @@
           <t>10.1080/13607863.2018.1531372</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="3" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>N=46, 均值67.17岁, 口头WM训练, RCT</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -874,9 +922,21 @@
           <t>10.1093/geronb/gbz073</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="3" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>E2-干预不符</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>BrainHQ为多域认知训练(处理速度为主)，WM非主要成分且未单独报告WM效果</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="n">
@@ -910,9 +970,17 @@
           <t>10.1037/pag0000895</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="3" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>N=76, 年龄60-85岁, 游戏化WM训练(n-back类), RCT+MRI</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -946,9 +1014,17 @@
           <t>10.1037/pag0000206</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="3" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>N=142, 均值70.35±3.66岁(65-80), WM训练(binding+spatial WM), Bayesian分析，无迁移效应</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -982,9 +1058,17 @@
           <t>10.3389/fnagi.2022.827188</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="3" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>N=54, 均值68.20±5.92岁, WM训练+tDCS, RCT - 已确认均值≥60</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1018,9 +1102,17 @@
           <t>10.3389/fnagi.2016.00049</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="3" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>约69.9岁, WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="n">
@@ -1054,9 +1146,17 @@
           <t>10.1016/j.brs.2016.04.001</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="3" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>约69.9岁, WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1090,9 +1190,17 @@
           <t>10.3389/fnagi.2019.00126</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="3" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>范围55-81岁，需找Table 1均值M判断</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -1126,9 +1234,17 @@
           <t>10.1155/2021/6664479</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="3" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>N=25, 均值68.84±4.65岁, VWM训练+tDCS, 含fMRI, 有行为结局</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -1162,9 +1278,17 @@
           <t>10.1016/j.jagp.2019.01.210</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="3" t="n"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>≥75岁，老年人，WM span</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1198,9 +1322,17 @@
           <t>10.3791/60804</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="3" t="n"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>66.7岁，n-back训练</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -1234,9 +1366,21 @@
           <t>10.1037/a0020683</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="3" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>均值27.0岁, n-back</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -1270,9 +1414,17 @@
           <t>10.1080/13825585.2013.790338</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="3" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>79.22岁(75-87岁)，WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1306,9 +1458,17 @@
           <t>10.1093/arclin/act020</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="3" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>均值未报告，年龄范围75-87岁(估算约81岁), WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -1342,9 +1502,17 @@
           <t>10.1007/s10339-020-00975-7</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="3" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>认知训练，需确认是否WM</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -1378,9 +1546,17 @@
           <t>10.1177/0091415017697725</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="3" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>N=86, 均值68.55岁(60-83), 空间WM+数字WM训练, RCT</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -1414,9 +1590,17 @@
           <t>10.1007/s11357-022-00538-y</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="3" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>均值71岁, WM span训练</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="n">
@@ -1450,9 +1634,17 @@
           <t>10.1016/j.cortex.2024.04.013</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="3" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>60-85岁，估算72.5岁，WM span训练</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="n">
@@ -1486,9 +1678,17 @@
           <t>10.3758/s13414-022-02580-6</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="3" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>N=104, 均值68.2岁, 视觉注意训练改善空间WM, 在线研究</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -1522,9 +1722,17 @@
           <t>10.1037/a0032982</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="3" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>65-95岁，估算80岁，WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="n">
@@ -1558,9 +1766,17 @@
           <t>10.2174/1874609812666190819125542</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="3" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>65-75岁，估算70岁，WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -1594,9 +1810,17 @@
           <t>10.1186/s13104-024-06844-2</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="3" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>60-75岁，估算67.5岁，WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="n">
@@ -1630,9 +1854,17 @@
           <t>10.1093/geronb/gbz090</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="3" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>N=183, 入组≥65岁(均值未在正文报告), n-back训练, RCT多中心</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -1666,9 +1898,17 @@
           <t>10.1007/s00426-014-0559-3</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="3" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>老年组N=65, 均值67.64-68.61岁(60-84), N-back WM训练, 含年轻-老年对比</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -1702,9 +1942,17 @@
           <t>10.1002/gps.4448</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="3" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>N=36(训练18+对照18), 均值69.50/69.77岁, WM span训练, 日常功能迁移</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -1738,9 +1986,17 @@
           <t>10.1002/gps.3859</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="3" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>均值70.0岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -1774,9 +2030,17 @@
           <t>10.1097/WNR.0000000000000080</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="3" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>N=40, 均值69.7岁(≥65), WM训练+tDCS, 10次session, 长期随访</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -1810,9 +2074,21 @@
           <t>10.1016/j.neuroimage.2013.07.069</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="3" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>E2-干预不符</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>三组训练任务均为Brain Fitness(听觉)/Space Fortress(游戏)/Road Tour(导航游戏)，均非WM主要训练</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -1846,9 +2122,17 @@
           <t>10.3389/fnagi.2022.1009262</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="3" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>N=28, 均值67.9±6.1岁(56-76), n-back WM训练+tDCS, 5天训练, 含行为结局</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -1882,9 +2166,17 @@
           <t>10.1080/1360786031000101175</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="3" t="n"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>均值83.5岁, WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="n">
@@ -1918,9 +2210,17 @@
           <t>10.1371/journal.pone.0101472</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="3" t="n"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>均值73.5岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -1954,9 +2254,21 @@
           <t>10.1162/jocn_a_01159</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="3" t="n"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>均值23.6岁(&lt;60岁), WM span</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="n">
@@ -1990,9 +2302,21 @@
           <t>https://doi.org/10.3389/fnagi.2018.00247</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="3" t="n"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>10-12岁(儿童), 非老年人研究</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -2026,9 +2350,17 @@
           <t>10.1037/a0014342</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="3" t="n"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>均值68.0岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="n">
@@ -2062,9 +2394,17 @@
           <t>10.3389/fpsyg.2023.1165275</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="3" t="n"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>均值70.0岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -2098,9 +2438,17 @@
           <t>10.3389/fnhum.2017.00085</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="3" t="n"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>均值66.0岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="n">
@@ -2134,9 +2482,21 @@
           <t>10.1037/neu0000088</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="3" t="n"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>20-31岁, 年轻人, 非老年人研究</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -2170,9 +2530,17 @@
           <t>10.1038/s41598-017-14030-7</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="3" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>均值64.27岁, WM训练+tDCS, COMT基因研究</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="n">
@@ -2206,9 +2574,17 @@
           <t>10.1007/s00426-025-02110-7</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="3" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>N=103, 均值70.57±5.5岁(60-84), 计算机化认知训练(含WM/n-back), RCT, 3个月干预</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -2242,9 +2618,17 @@
           <t>255</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="3" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>均值75.8岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="2" t="n">
@@ -2278,9 +2662,17 @@
           <t>10.3389/fnagi.2013.00020</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="3" t="n"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>N=30(训练19+对照11), 均值69.89/71.06岁(64-79), WM span训练(听觉+视空间), 5周在线, 含6月随访</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -2314,9 +2706,17 @@
           <t>10.3389/fnagi.2018.00112</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="3" t="n"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>N=97, 入组≥65岁(均值未报告), WM训练(n-back, BrainGymmer), 8周, 含主观+客观认知结局</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="2" t="n">
@@ -2350,9 +2750,17 @@
           <t>10.1186/s12877-025-06507-2</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="3" t="n"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>均值69.5岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -2386,9 +2794,17 @@
           <t>10.3389/fnagi.2017.00039</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="3" t="n"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>均值75.0岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="2" t="n">
@@ -2422,9 +2838,17 @@
           <t>10.1159/000324240</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="3" t="n"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>均值80.0岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -2458,9 +2882,17 @@
           <t>10.3389/fpsyg.2016.00230</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="3" t="n"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>N=43, 均值68.81±5.18岁(60-86), WM更新训练(N-Match任务), RCT双盲</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="2" t="n">
@@ -2494,9 +2926,17 @@
           <t>https://doi.org/10.1016/j.nbas.2023.100083</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="3" t="n"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>N=119, 均值72.86±5.14岁(65-85), n-back WM训练+元认知研讨会(EngAge), 20次session, 含3月随访</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -2530,9 +2970,17 @@
           <t>10.3389/fnhum.2017.00099</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="3" t="n"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>N=148(四研究合并), 均值71.63±5.53岁(61-87), verbal WM span训练, 分析个体特征对训练效果的调节作用</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="2" t="n">
@@ -2566,9 +3014,17 @@
           <t>10.3389/fneur.2021.625359</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="3" t="n"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>均值69.0岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -2602,9 +3058,17 @@
           <t>10.1002/trc2.12262</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="3" t="n"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>N=51, 均值70±4岁(65-80), WM训练+tDCS, RCT, 含随访</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="n">
@@ -2638,9 +3102,21 @@
           <t>10.3389/fnagi.2010.00027</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="3" t="n"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>均值25.5岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -2674,9 +3150,17 @@
           <t>10.3389/fnhum.2014.00617</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="3" t="n"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>均值75.6岁, WM span</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="n">
@@ -2710,9 +3194,21 @@
           <t>10.1038/s41539-025-00369-4</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="n"/>
-      <c r="J59" s="3" t="n"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>均值54.5岁, 元认知训练</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -2746,9 +3242,17 @@
           <t>10.3389/fnagi.2021.718965</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="3" t="n"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>N=24, 均值68.83±2.85岁(64-75), WM span训练, 含静息态EEG, pilot研究</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="n">
@@ -2782,9 +3286,17 @@
           <t>10.1007/s00426-026-02249-x</t>
         </is>
       </c>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="3" t="n"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>N=66, 均值69.58±7.04岁, 单域WM训练(n-back) vs 多域EF训练 vs 主动对照, 4周, Bayesian分析</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -2818,9 +3330,17 @@
           <t>https://doi.org/10.1016/j.psfr.2017.04.005</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="3" t="n"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>均值69.0岁, 策略训练</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="n">
@@ -2854,9 +3374,17 @@
           <t>https://doi.org/10.1080/20445911.2020.1833891</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="3" t="n"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>均值63.71岁, 策略训练</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -2890,9 +3418,17 @@
           <t>https://doi.org/10.1002/acp.3126</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="3" t="n"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>均值66.85岁, 策略训练</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="n">
@@ -2926,9 +3462,21 @@
           <t>https://doi.org/10.5114/hpr.2016.56846</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="3" t="n"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>均值37.87岁, 策略训练</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="n">
@@ -2962,9 +3510,21 @@
           <t>10.1038/s41562-022-01384-w</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="3" t="n"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>均值20.1岁, 策略训练</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="n">
@@ -2998,9 +3558,21 @@
           <t>10.1371/journal.pone.0050431</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="3" t="n"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>训练组均值25.36岁，对照组25.49岁，为年轻人样本，非老年人</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -3034,9 +3606,17 @@
           <t>10.1007/s41465-026-00354-8</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="3" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>均值70.0岁, 策略训练</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="n">
@@ -3070,9 +3650,21 @@
           <t>10.1007/s12144-022-03363-w</t>
         </is>
       </c>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="6" t="n"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>均值32.0岁, n-back</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="n">
@@ -3106,9 +3698,21 @@
           <t>10.12982/JAMS.2025.065</t>
         </is>
       </c>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="6" t="n"/>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>均值58.0岁, WM训练</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="n">
@@ -3142,9 +3746,21 @@
           <t>10.1017/S0033291726103298</t>
         </is>
       </c>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="6" t="n"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>E1-人群不符</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>PTSD退伍军人样本，三组均值38-41岁，非健康老年人(≥60岁)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="n">
@@ -3178,9 +3794,21 @@
           <t>10.14257/ijgdc.2017.10.10.05</t>
         </is>
       </c>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="6" t="n"/>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>E4-研究设计不符</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>软件/系统设计论文，介绍n-back训练程序内容，无实证研究数据，无参与者</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J72"/>

--- a/projects/paper-01/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-01/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -1192,13 +1192,13 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>不确定</t>
+          <t>纳入</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>范围55-81岁，需找Table 1均值M判断</t>
+          <t>N=83, 入组≥60岁(波兰), MMSE≥27, dual n-back训练, 25sessions, 均值未报告</t>
         </is>
       </c>
     </row>
